--- a/光伏配储项目/电价数据/2026/栗源光伏电站.xlsx
+++ b/光伏配储项目/电价数据/2026/栗源光伏电站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.33722</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.99238</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.38561</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.39993</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.36665</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.40925</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.35356</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.3430299999999999</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.34384</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.33508</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.33742</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.36211</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.36171</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.36873</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.36838</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.36762</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.2982</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30338</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.30309</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.30247</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.2575</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.28016</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.2453</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.26073</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.26409</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.27347</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.31715</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07156</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.22293</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.1744</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.26445</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.26855</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.26858</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21981</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.18336</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.30778</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.30892</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.2891</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.28883</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.30179</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.31755</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.35414</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.64688</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.82547</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.36726</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.4259</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.47602</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.51085</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.76063</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.17517</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.55767</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.56619</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.57072</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.39277</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.61956</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.75085</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.58314</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.89973</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.99517</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.40862</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.12345</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.01671</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.96216</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.62214</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.5826</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.5532899999999999</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.48913</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.5039</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7807799999999999</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.02729</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.11695</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5001100000000001</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52485</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.51132</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50743</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48902</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47071</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37736</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.43274</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.36977</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.42246</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.40506</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.36369</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.35428</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.44342</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.34287</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.42068</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.42585</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.6069</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.54584</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.5744900000000001</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.27996</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.31489</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.3003</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.30159</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.29655</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.22803</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.5488500000000001</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.43754</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.38752</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.38041</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.31522</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.59588</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.8008</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.5920800000000001</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.7097899999999999</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.7422000000000001</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.36906</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.41341</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.9061</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.54256</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.34792</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.54485</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.16857</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.37654</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.69269</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.16397</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.9071900000000001</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.1984</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.10277</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.30254</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.91171</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.43959</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.89071</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.89835</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44493</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42552</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44525</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37954</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33631</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50934</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48738</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.5591499999999999</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.42885</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.4489</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.4179</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38335</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39299</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47387</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39873</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.37043</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.35533</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.37196</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.71785</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.60633</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.38177</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.6080800000000001</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.77362</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.7752899999999999</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.7467200000000001</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.7845299999999999</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.85125</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.90154</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.90985</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.01955</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.49816</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.51959</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.72441</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.7410800000000001</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.6166799999999999</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.6263099999999999</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.49985</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.6416799999999999</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.3423</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45016</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.49781</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.50029</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.56196</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.5814900000000001</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.50817</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.52155</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.00394</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.5777599999999999</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.69523</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.45414</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50369</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.46893</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.5549299999999999</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.47719</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.6691699999999999</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.38032</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.46905</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.40706</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.46326</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.54526</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.5721799999999999</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.52174</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.68029</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.57759</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.53203</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.4546</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.60942</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.4169</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.44097</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.38921</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3432</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.56638</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.54896</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.47985</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39806</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.41013</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36799</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.41012</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.40654</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.37183</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.48962</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36852</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36513</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36779</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.3663</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.39387</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.40965</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37812</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.37913</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41578</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.42516</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.45598</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.49318</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.37913</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.37777</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.5288999999999999</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.49049</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.4809</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37721</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.19339</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.27501</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.82612</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.39481</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.38378</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.50495</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.29731</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.40373</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.36782</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.36824</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.22156</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.38226</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.35245</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.40264</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.46842</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.2759</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.42553</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.41624</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.38658</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.41758</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.43606</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.51988</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.41967</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.66518</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.4716</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.44441</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50226</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.42619</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.40758</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.38833</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.3835</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.37404</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.35332</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32366</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29225</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.37142</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37566</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37156</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31334</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31484</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31574</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28819</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.27901</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.29979</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.13347</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.30491</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.01779</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.29863</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.29207</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.28233</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.29741</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.40009</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.37874</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.2646</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25535</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.22966</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.09556000000000001</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.30434</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.26936</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.04615</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.27494</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30199</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30485</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34893</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.35386</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.3711</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.4397799999999999</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36867</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.36379</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.44295</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34296</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35188</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31973</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.30751</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.25575</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.22783</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.31203</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.29297</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.20322</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.25744</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.14912</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.25895</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.0329</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.30009</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30723</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.16901</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.25418</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.22363</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.20214</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.24828</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.18493</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30754</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.25568</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.27636</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.2115</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.27068</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.1025</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04789</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04924</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.31692</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00438</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20202</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04466</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27174</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19132</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.008230000000000001</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.0551</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05509</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14031</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.31766</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.30387</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.26884</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.30966</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.16984</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15646</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1686</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14582</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15718</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15646</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.2327</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.2119</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22474</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.2797</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.2697</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37645</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.4305</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.47006</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.42665</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.36261</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40799</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15669</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50763</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62201</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49794</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78099</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92031</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.4945</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91412</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8630599999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29609</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88742</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63152</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18698</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87036</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.66251</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33078</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03284</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53074</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.57563</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77754</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49315</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44999</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.2071</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87899</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5511200000000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62191</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5384</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49776</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45589</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42432</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43721</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38823</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45275</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41985</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39336</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37843</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38954</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.40089</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37569</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32118</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32372</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.32147</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44426</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.45935</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.53225</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60253</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.84785</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.41464</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.30401</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.46304</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.34091</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.53779</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.76416</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87898</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.33413</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.6162000000000001</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29223</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.43751</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.4915</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.31714</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31002</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32449</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30718</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28725</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29535</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30596</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29548</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30373</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.18921</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.2658</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.26587</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.27817</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.27792</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.29581</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.31028</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.30225</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.29662</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.29582</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.3132200000000001</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.29634</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.32627</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1.19445</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.31091</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.38987</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.33333</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.34672</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.34321</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.30097</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.30231</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.30345</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.29386</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.31104</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.30696</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.30101</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.30118</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.30297</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.30499</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.29815</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.26448</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29514</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.30054</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.29327</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30432</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30207</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.26271</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31082</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.39007</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30173</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.28423</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.29649</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.38177</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.25558</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.4612</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.26343</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.28702</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29909</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.27385</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.26021</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.28257</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.28308</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.24209</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.24164</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.21865</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.20307</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.19882</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.22163</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.12634</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.21695</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.10183</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.19015</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.19174</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.17062</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.19526</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.27177</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.2814</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.23242</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.27849</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.26366</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.27942</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.28051</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.25508</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.27042</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.27468</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.27345</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.25714</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.27851</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.28227</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.29353</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.28766</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.2854</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.30438</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.29102</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.38732</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.29899</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.35696</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.27538</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.3027</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.28598</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.29652</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.16573</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.6163099999999999</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.33181</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.7857499999999999</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.52807</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.68399</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.49128</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.18174</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.1699</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.35743</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.40755</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.32826</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.36614</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.29401</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.40224</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.28913</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.28909</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.39546</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.29289</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.29033</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.27761</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.28251</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.36433</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.13223</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.20787</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.20618</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.29711</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.27585</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.29416</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.2801</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.21492</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.26318</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.32678</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.40325</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.30278</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.23401</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.26775</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.26331</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.26922</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.26209</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.28476</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.29777</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.28548</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.23043</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.18524</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.28392</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.26536</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.20556</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.22202</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.26058</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.23561</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.28446</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.2853</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.20909</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.28635</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.2348</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.26741</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.31279</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.31186</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.26024</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.28991</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.28861</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.26994</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.26123</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.29595</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.31726</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.5855399999999999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.31703</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.31731</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.36189</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.31283</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.29236</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.25799</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.28853</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.23638</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.26443</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.24489</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.23801</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.1571</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30825</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.19878</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.17799</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.19577</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.15357</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.22233</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.24081</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.24007</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.27421</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.27042</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.11053</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.1138</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.22208</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.23443</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.26568</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.02028</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.13342</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.20298</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.02134</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.16596</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.16295</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.18104</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.25554</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.27652</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.19462</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.26489</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.16038</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.28206</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.18515</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.27124</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.14369</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.22305</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.28552</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.29315</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.27129</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.30208</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.28262</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29374</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.27929</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.26652</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.28294</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.2652</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.26057</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.28059</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.30485</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.29156</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.28448</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.28979</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.30777</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.30871</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.27919</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.30913</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.30729</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.29668</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.29685</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.29694</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.30021</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.29834</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.30254</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.30932</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.29781</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.2962</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.29688</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.30135</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.29698</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.30338</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.31497</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.29913</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.30514</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.30907</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.47568</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.35345</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.29076</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.29322</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.25708</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.28695</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.29413</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.39621</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.33404</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.30717</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38193</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36604</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.32424</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.30356</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.29967</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29916</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.30334</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.29875</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29741</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29913</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29741</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.30384</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.30076</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.30405</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.29413</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29567</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.29886</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30698</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.30124</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30908</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.32561</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.30968</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.31537</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30991</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.3139</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30815</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.32371</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30241</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.32392</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30412</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.33813</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.45516</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.37201</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.41899</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.35779</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.42718</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.5532</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.4773</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.39605</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.36321</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41788</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.33499</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36391</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.29432</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.32272</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.31496</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.31254</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.31441</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3563</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.3058999999999999</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.29357</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.29762</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.29067</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.29414</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.29694</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.30037</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.30285</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.29804</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29852</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.29833</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.29622</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.31232</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30708</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.29807</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29923</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.2957</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31408</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.31109</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29821</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.30903</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.54147</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.55098</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.15872</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.49018</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.7415</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.50143</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.46208</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.6456000000000001</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.76598</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.49952</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.60287</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.40552</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.9295800000000001</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27888</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.38537</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.52915</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.42636</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.42524</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.16756</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.45657</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.37898</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.61403</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.57162</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.56063</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.91696</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.6018300000000001</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.6040399999999999</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.69141</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.52558</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.64937</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.40949</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.36377</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.36355</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.41022</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.43947</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.38776</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.83861</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.65298</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.58953</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.8272699999999999</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.40583</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.69702</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.38485</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.34219</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.30824</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.46972</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.29803</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.28444</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.29885</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.23426</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.2889</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.0373</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.17644</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30895</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38584</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.28495</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.2805299999999999</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.28331</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.28406</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.20751</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.19765</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.27583</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.27874</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.27689</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.27493</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.2747</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.27628</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.20039</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29618</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.19792</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.1635</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.23992</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.29233</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.29503</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.26611</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.19792</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.20398</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.17172</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.21097</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.17763</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.16892</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.20873</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.23238</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.27831</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.31563</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.29632</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.34538</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.28888</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.3142200000000001</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.28942</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.28205</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.28896</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.28332</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.3042</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.2785</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.24939</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.28261</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.2983</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.27741</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.28981</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.28918</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.29856</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.28275</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.26465</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.23838</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.2558</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.26179</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.16774</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.2796</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.3416</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.29516</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.30083</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.2798</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.29362</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.32266</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.31288</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.29821</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.30277</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.27871</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.28944</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.29048</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.28171</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.29218</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.27305</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.23838</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.31572</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.2845</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.1629</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.13576</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.24216</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.32127</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.29581</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.28553</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.00708</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.29395</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.28996</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.27749</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.3119</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3119</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.28931</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.28919</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29625</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.28675</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.31193</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.2882</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.28882</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.27751</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.28769</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.29395</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.29348</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.28395</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.27743</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.28846</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.29532</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.27745</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.28773</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29639</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.29337</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.30119</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30862</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31685</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30196</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31353</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30676</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30862</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30619</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.3088</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32257</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32122</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32766</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36215</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36316</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.33228</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.49949</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.32489</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.96348</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.95826</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.40831</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.36393</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.37784</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.30016</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.38366</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.34827</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.2892</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.31409</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.32363</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30948</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.41645</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32686</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.32977</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.32656</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.34179</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.35188</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.5048</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.40464</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.45763</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.38173</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.34735</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.42133</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.67545</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.5022099999999999</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.05906</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.97836</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.05282</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.27757</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.38799</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.5794900000000001</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.51615</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.73834</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.54128</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.67972</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.41581</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.32383</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.32459</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.31737</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.34721</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.36756</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.38687</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36935</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.34337</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.31772</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.31744</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.3147799999999999</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.2953</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.30253</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.29339</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.43675</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.44489</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.42973</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.51344</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.56548</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.6224</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.5561200000000001</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.3784</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.34803</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.36548</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.33713</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.35671</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.44818</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.65352</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.98162</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.39322</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.48991</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.32797</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.28582</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.30786</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.29885</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.34299</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.42007</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.35322</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.39656</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.39034</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.41826</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.94023</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.71736</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6488700000000001</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.36694</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.33859</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.33319</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.35247</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.41211</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.39237</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.28477</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.29733</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.30265</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.32218</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.32066</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.31166</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33815</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.02417</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.2824</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.28919</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33815</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.28433</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.29048</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.29715</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32759</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.36334</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.37056</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.34242</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.38895</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.37523</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.35752</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.38097</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.38322</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.38322</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.42781</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.38739</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.42697</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.42378</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.42705</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.34849</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.31574</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.29466</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.30505</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.30295</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.30686</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.30542</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.36374</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.30387</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.20342</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.36948</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.30516</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37237</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.28476</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.19185</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.19244</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.21271</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.24328</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.23702</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.18872</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.27434</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.29339</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.2875</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.17809</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.29748</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.16858</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.189</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.17967</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.18984</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.19029</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.30396</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.27012</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.23231</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.22951</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.17931</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.02451</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.25867</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.02122</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.02046</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.17885</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.01037</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.20907</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.17931</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.01758</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.16842</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.17358</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.20579</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.17071</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.17358</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.17645</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.01585</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.17931</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.01565</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.00775</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.19077</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.19112</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.16046</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.28554</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.01964</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.2536</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.30207</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.27132</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.18341</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28375</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.24044</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.20895</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29848</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.3088</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.06636</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.30463</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.00349</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28647</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.32558</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3066</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30258</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.27799</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.30386</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.30637</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.30522</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.2803</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.29219</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30355</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.30272</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.30595</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.32655</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.31237</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.30616</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.28462</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.26353</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.29589</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.30566</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.30609</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.28237</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.26491</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.27769</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.27675</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.2644</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.22551</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.21711</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.2128</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.25511</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.26829</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.26035</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.25883</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.18037</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.18657</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.26035</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.16791</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.28237</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.16791</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.23684</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.23701</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.2927</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.28139</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.28122</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.28788</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.2795299999999999</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.06283</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.1961</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.19275</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.27288</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.01092</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.21142</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.23106</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.22131</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.05248</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.00193</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.01089</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.01089</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.01021</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.01021</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.01062</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.20428</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.00257</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.01021</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.01028</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.18519</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.0019</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.00194</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30649</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.01184</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.00355</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.2464</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.04404</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.00549</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00034</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.12369</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02201</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01834</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04297</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04089</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02935</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04408</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00547</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27029</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04934</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.04105</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03595</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03757</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.1906</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.25917</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.27988</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27328</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.27608</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.28555</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.28245</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.3057</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.29962</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28374</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29669</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.29445</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29827</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30401</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29692</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.31004</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.29624</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.30023</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.27447</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.3733399999999999</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.30657</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.04918</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.28853</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.31333</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.29686</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.28608</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.18305</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.17729</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.18178</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.17901</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.008140000000000001</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.16313</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.00715</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.03822</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.0355</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.01007</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.00631</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.04184</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.02009</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.02261</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.02733</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.42255</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.20792</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.28212</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.32566</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.01002</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.24738</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.01385</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.36184</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.85505</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8568</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.35674</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.08604000000000001</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.00696</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.25715</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28318</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.31208</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.29119</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.43174</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.28884</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29031</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-1e-05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29013</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00158</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31474</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.30803</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06637</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.30537</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.29774</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30397</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.2504</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.2904</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.46845</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31592</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32382</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33296</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.31603</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32391</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33299</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.9756699999999999</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.6629299999999999</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.44551</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.50959</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.11019</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.17861</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.45821</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.77512</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.53984</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.03748</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.03748</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1.03963</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.17922</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.44842</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.54425</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.46638</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.35229</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.31477</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.31477</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35306</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.38452</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.04307</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.53665</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.29962</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.2804</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35928</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.27326</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.20642</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.26573</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.26276</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.25434</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.2251</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.27686</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.21282</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.18075</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.20825</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.17502</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.1775</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.008070000000000001</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.1748</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.1961</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.2448</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.27681</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.27673</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.22531</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.24364</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.28446</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.23037</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.26527</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.31366</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.33315</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.30564</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31099</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26899</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.3151600000000001</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.3137799999999999</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31763</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32258</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.32666</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.3252</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.32767</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35229</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.41912</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.3789</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.40515</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35709</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35725</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.36297</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31713</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.31482</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.30219</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.29779</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.2987</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37929</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.37848</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.36925</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.33477</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32826</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.30559</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.30523</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.29804</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.30164</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.30358</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.30358</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.31112</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.30521</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.31689</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.31622</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.31557</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.31495</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.36128</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.75275</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.5454600000000001</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.36902</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.33311</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.32333</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33224</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30126</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33536</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.3746</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32654</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.52888</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.45954</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.54164</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.04091</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.09957</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.45896</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.36546</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.6260599999999999</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.92871</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.07967</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.47196</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.83323</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.42855</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.35601</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.42631</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.35583</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.33619</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32428</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.32162</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.32097</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.44227</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34782</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.3258</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.3096</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.30348</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.3088</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.30398</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.30398</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.29811</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.29864</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.34398</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.37489</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.41181</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.39406</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.36219</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.38101</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.34601</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.37254</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.35559</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.34205</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.35787</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.38956</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.38202</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.3535</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42314</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.40439</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.71523</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.78076</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.26121</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.83824</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.21851</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.64402</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.90839</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.7655</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.54962</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.18435</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.03225</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.12736</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.9568099999999999</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.77385</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.36703</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.47419</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.36465</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.32853</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.2866</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.29111</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.30249</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.29638</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.3052</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.2962</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.3141600000000001</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.30899</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30789</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.006730000000000001</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.2981</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29527</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.29153</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31942</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.29769</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.29017</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30845</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.31565</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.25975</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.3474100000000001</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.30107</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.5355599999999999</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.19718</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29161</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.41583</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.54883</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.33797</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.32409</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.30121</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.32827</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.31539</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.37946</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.58189</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36431</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.42283</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.33817</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.37463</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.48016</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.38774</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.5972799999999999</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.47719</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.6073999999999999</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.8405499999999999</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.47355</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.6326000000000001</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.49655</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.53801</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.3752200000000001</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.37521</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.35305</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.35402</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.33035</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.33412</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.95989</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.45265</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.5808300000000001</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.50041</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.47869</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.35265</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.36736</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.35882</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.35745</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.37154</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36387</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.3467</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.36207</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.36255</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36348</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35256</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35228</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.36461</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.34742</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.34276</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.34368</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33784</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.4342</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.38753</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.34474</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.4686</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.5701799999999999</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32771</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.35275</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.38694</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.37332</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.3422</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.35349</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.36523</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.34672</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.34812</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.5351</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.71324</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.5205599999999999</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.38806</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.48302</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.5130800000000001</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.42905</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.34322</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.34222</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.37386</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.37057</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37191</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34526</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33814</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.34184</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34601</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33192</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33749</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33499</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33192</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.33291</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31075</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31562</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17908</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30617</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29702</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14637</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.20099</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14208</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.2898</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.11632</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.2261</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26698</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14613</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14337</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.2878</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18866</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22998</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26837</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.1569</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.16014</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30914</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20108</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.20479</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.29402</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.29177</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.32766</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.35409</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.37537</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.41704</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.39069</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.32735</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.41037</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.36715</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36083</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.36426</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.36621</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.4082</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.37424</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.37527</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.36248</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.36356</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.3533</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.35838</v>
       </c>
     </row>
   </sheetData>
